--- a/docs/modelling_approach.xlsx
+++ b/docs/modelling_approach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johtorr/Documents/Repos/neural_networks_project_hdm/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7F4CDB-7D8E-8E4A-AED6-4A85D9E4FD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00DE679-506F-9D46-B0F8-AF7E92F6FBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
     <sheet name="Tabelle3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -413,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -436,20 +436,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1239,33 +1238,33 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="9" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="12" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="O10" s="16" t="s">
+      <c r="O10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="O11" s="15"/>
+      <c r="O11" s="14"/>
     </row>
     <row r="12" spans="2:19" ht="17" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
@@ -1296,20 +1295,18 @@
       <c r="H14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="O14" s="12"/>
     </row>
     <row r="15" spans="2:19" ht="17" x14ac:dyDescent="0.25">
-      <c r="H15" s="12"/>
       <c r="O15" s="11"/>
     </row>
     <row r="16" spans="2:19" ht="17" x14ac:dyDescent="0.25">
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="O16" s="14" t="s">
+      <c r="O16" s="13" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1399,12 +1396,6 @@
       </c>
       <c r="O24" s="11"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="O25" s="12"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="H27" s="12"/>
-    </row>
     <row r="28" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
         <v>33</v>
@@ -1417,13 +1408,13 @@
       </c>
     </row>
     <row r="29" spans="2:15" ht="17" x14ac:dyDescent="0.25">
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="O29" s="14" t="s">
+      <c r="O29" s="13" t="s">
         <v>41</v>
       </c>
     </row>

--- a/docs/modelling_approach.xlsx
+++ b/docs/modelling_approach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johtorr/Documents/Repos/neural_networks_project_hdm/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00DE679-506F-9D46-B0F8-AF7E92F6FBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7D79D5-6B83-DF40-9666-F8D33C05C5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
   </bookViews>
@@ -187,9 +187,6 @@
     <t>Multivariate Timeseries Using Flattenned-Batch Approach</t>
   </si>
   <si>
-    <t>Each sample represents ALL timeseries at ONE time window</t>
-  </si>
-  <si>
     <t>        = (6, 4002)</t>
   </si>
   <si>
@@ -248,18 +245,6 @@
   </si>
   <si>
     <t>  ...</t>
-  </si>
-  <si>
-    <t>  [[1234.5], [1245.2], [1256.8], [1267.3], [1278.9], [1289.1]],  # Series 0: t-5 to t</t>
-  </si>
-  <si>
-    <t>  [[2341.2], [2356.7], [2372.1], [2387.4], [2402.8], [2418.3]],  # Series 1: t-5 to t</t>
-  </si>
-  <si>
-    <t>  [[3456.8], [3478.9], [3501.2], [3523.6], [3546.1], [3568.7]],  # Series 2: t-5 to t</t>
-  </si>
-  <si>
-    <t>  [[9876.5], [9912.3], [9948.7], [9985.2], [10022], [10059]]     # Series 999: t-5 to t</t>
   </si>
   <si>
     <t>[1302.4, 2433.9, 3591.4, ..., 10096]</t>
@@ -317,6 +302,21 @@
   </si>
   <si>
     <t>        = (1502, 6, 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each sample represents ALL timeseries at ONE time window. All series flattened per time window. </t>
+  </si>
+  <si>
+    <t>  [[val_0, gdp_0,…, cpi_0], ..., [[val_5, gdp_5,…, cpi_5]]],  # Series 0: t-5 to t</t>
+  </si>
+  <si>
+    <t>  [[val_0, gdp_0,…, cpi_0], ..., [[val_5, gdp_5,…, cpi_5]]],  # Series 1: t-5 to t</t>
+  </si>
+  <si>
+    <t>  [[val_0, gdp_0,…, cpi_0], ..., [[val_5, gdp_5,…, cpi_5]]],  # Series 2: t-5 to t</t>
+  </si>
+  <si>
+    <t>  [[val_0, gdp_0,…, cpi_0], ..., [[val_5, gdp_5,…, cpi_5]]]     # Series 1501: t-5 to t</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1245,7 @@
         <v>36</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1253,10 +1253,10 @@
         <v>34</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
@@ -1274,7 +1274,7 @@
         <v>32</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="17" x14ac:dyDescent="0.25">
@@ -1282,18 +1282,18 @@
         <v>31</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="2:19" ht="17" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="17" x14ac:dyDescent="0.25">
@@ -1301,13 +1301,13 @@
     </row>
     <row r="16" spans="2:19" ht="17" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="O16" s="13" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="17" x14ac:dyDescent="0.25">
@@ -1323,65 +1323,65 @@
     </row>
     <row r="18" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O23" s="11" t="s">
         <v>28</v>
@@ -1401,10 +1401,10 @@
         <v>33</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="17" x14ac:dyDescent="0.25">
@@ -1412,10 +1412,10 @@
         <v>35</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="17" x14ac:dyDescent="0.25">
@@ -1423,10 +1423,10 @@
         <v>29</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:15" ht="17" x14ac:dyDescent="0.25">

--- a/docs/modelling_approach.xlsx
+++ b/docs/modelling_approach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johtorr/Documents/Repos/neural_networks_project_hdm/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7D79D5-6B83-DF40-9666-F8D33C05C5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D9B0E3-2030-424D-9C97-D0F02D64B7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
   </bookViews>
@@ -226,24 +226,6 @@
     <t>Example X for ALL timeseries (timestep t-5 to t):</t>
   </si>
   <si>
-    <t>  [val_(t-4), gdp, cpi, … , 2023, 2],  # t-4</t>
-  </si>
-  <si>
-    <t>  [val_(t-5), gdp, cpi, … , 2023, 1],  # t-5</t>
-  </si>
-  <si>
-    <t>  [val_(t-3), gdp, cpi, …, 2023, 2],  # t-3</t>
-  </si>
-  <si>
-    <t>  [val_(t-2), gdp, cpi, …, 2023, 2],  # t-2</t>
-  </si>
-  <si>
-    <t>  [val_(t-1), gdp, cpi, …, 2023, 2],  # t-1</t>
-  </si>
-  <si>
-    <t>  [val_(t).  , gdp, cpi, …, 2023, 2],  # t</t>
-  </si>
-  <si>
     <t>  ...</t>
   </si>
   <si>
@@ -301,9 +283,6 @@
     <t>Example X for ALL timeseries (series dimension first):</t>
   </si>
   <si>
-    <t>        = (1502, 6, 1)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Each sample represents ALL timeseries at ONE time window. All series flattened per time window. </t>
   </si>
   <si>
@@ -317,6 +296,27 @@
   </si>
   <si>
     <t>  [[val_0, gdp_0,…, cpi_0], ..., [[val_5, gdp_5,…, cpi_5]]]     # Series 1501: t-5 to t</t>
+  </si>
+  <si>
+    <t>  [val_(t-5), gdp, cpi, … , 2023, 1, …, 1, 0],  # t-5</t>
+  </si>
+  <si>
+    <t>  [val_(t-4), gdp, cpi, … , 2023, 2, …, 1, 0],  # t-4</t>
+  </si>
+  <si>
+    <t>  [val_(t-3), gdp, cpi, …, 2023, 3, …, 1, 0],  # t-3</t>
+  </si>
+  <si>
+    <t>  [val_(t-2), gdp, cpi, …, 2023, 4, …, 1, 0],  # t-2</t>
+  </si>
+  <si>
+    <t>  [val_(t-1), gdp, cpi, …, 2023, 5, …, 1, 0],  # t-1</t>
+  </si>
+  <si>
+    <t>  [val_(t).  , gdp, cpi, …, 2023, 6, …, 1, 0],  # t</t>
+  </si>
+  <si>
+    <t>        = (1502, 6, n_features)</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1245,7 @@
         <v>36</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1253,10 +1253,10 @@
         <v>34</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
@@ -1274,7 +1274,7 @@
         <v>32</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="17" x14ac:dyDescent="0.25">
@@ -1285,7 +1285,7 @@
         <v>41</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="2:19" ht="17" x14ac:dyDescent="0.25">
@@ -1307,7 +1307,7 @@
         <v>49</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="17" x14ac:dyDescent="0.25">
@@ -1323,62 +1323,62 @@
     </row>
     <row r="18" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>44</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>42</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>43</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>45</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>46</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>47</v>
@@ -1401,10 +1401,10 @@
         <v>33</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="17" x14ac:dyDescent="0.25">
@@ -1426,7 +1426,7 @@
         <v>38</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="2:15" ht="17" x14ac:dyDescent="0.25">
@@ -1437,5 +1437,6 @@
     <mergeCell ref="O10:S10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/docs/modelling_approach.xlsx
+++ b/docs/modelling_approach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johtorr/Documents/Repos/neural_networks_project_hdm/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D9B0E3-2030-424D-9C97-D0F02D64B7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25AC5E2-27EA-8F44-8B82-DD0563CAAC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
   </bookViews>
@@ -1234,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C4425D2-5FFA-4C4B-A495-A22788A789E5}">
-  <dimension ref="B9:S31"/>
+  <dimension ref="B9:S29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="9" spans="2:19" x14ac:dyDescent="0.2">
@@ -1396,41 +1396,41 @@
       </c>
       <c r="O24" s="11"/>
     </row>
+    <row r="26" spans="2:15" ht="17" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" ht="17" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="28" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="17" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="O29" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" ht="17" x14ac:dyDescent="0.25">
-      <c r="B30" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="O30" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" ht="17" x14ac:dyDescent="0.25">
-      <c r="O31" s="11"/>
+      <c r="O29" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/modelling_approach.xlsx
+++ b/docs/modelling_approach.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johtorr/Documents/Repos/neural_networks_project_hdm/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25AC5E2-27EA-8F44-8B82-DD0563CAAC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F703579C-52D6-BB44-9625-CD27C9C95A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
-    <sheet name="Tabelle3" sheetId="3" r:id="rId3"/>
+    <sheet name="Tabelle4" sheetId="4" r:id="rId2"/>
+    <sheet name="Tabelle2" sheetId="2" r:id="rId3"/>
+    <sheet name="Tabelle3" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>Date</t>
   </si>
@@ -89,24 +90,6 @@
   </si>
   <si>
     <t>Model</t>
-  </si>
-  <si>
-    <t>RNN-Uni-Exog</t>
-  </si>
-  <si>
-    <t>RNN-Uni</t>
-  </si>
-  <si>
-    <t>Tat</t>
-  </si>
-  <si>
-    <t>Vor</t>
-  </si>
-  <si>
-    <t>mitt. SMAPE</t>
-  </si>
-  <si>
-    <t>RNN-Multi-Exog</t>
   </si>
   <si>
     <t>Train</t>
@@ -318,12 +301,267 @@
   <si>
     <t>        = (1502, 6, n_features)</t>
   </si>
+  <si>
+    <t>MSE</t>
+  </si>
+  <si>
+    <t>Exog</t>
+  </si>
+  <si>
+    <t>Fold1</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>SMAPE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**MLP**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Multi-Layer Perceptron (fully connected feedforward network)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**RNN**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Recurrent Neural Network (vanilla architecture with recurrent connections)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**LSTM**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Long Short-Term Memory (RNN with gating mechanisms for long-term dependencies)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**GRU**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Gated Recurrent Unit (simplified LSTM variant with fewer parameters)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**Transformer**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Self-attention-based architecture for sequence modeling</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**CNN1D**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: One-Dimensional Convolutional Neural Network (temporal pattern extraction)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**N-BEATS**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Neural Basis Expansion Analysis for Time Series (interpretable deep learning)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>**N-BEATSx**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>: N-BEATS with exogenous variable support</t>
+    </r>
+  </si>
+  <si>
+    <t>Approach</t>
+  </si>
+  <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>Uni</t>
+  </si>
+  <si>
+    <t>Multi</t>
+  </si>
+  <si>
+    <t>no Exog</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>RNN</t>
+  </si>
+  <si>
+    <t>LSTM</t>
+  </si>
+  <si>
+    <t>GRU</t>
+  </si>
+  <si>
+    <t>Transformer</t>
+  </si>
+  <si>
+    <t>CNN1D</t>
+  </si>
+  <si>
+    <t>N-BEATS</t>
+  </si>
+  <si>
+    <t>N-BEATSx</t>
+  </si>
+  <si>
+    <t>Fold</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -374,6 +612,25 @@
       <color theme="1"/>
       <name val="Aptos Narrow (Textkörper)"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -413,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -450,6 +707,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -784,248 +1042,362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82464023-9D77-A249-8041-873460035956}">
-  <dimension ref="B4:J31"/>
+  <dimension ref="B4:L34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>0</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>2</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>3</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>7</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>8</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>9</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>10</v>
       </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>6</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>2020</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>1</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>12</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>6</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>2020</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>12</v>
       </c>
-      <c r="J12" t="s">
+      <c r="L12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>6</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>2020</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13">
+        <v>2020</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>12</v>
       </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>6</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>2020</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>2</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>12</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C17" t="s">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
         <v>13</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="D18" t="s">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G20" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>1502</v>
-      </c>
-      <c r="C21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21">
-        <v>100</v>
-      </c>
-      <c r="H21">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>16</v>
       </c>
-      <c r="I22">
-        <f>(G21-H21)/G21</f>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="L22" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31">
-        <v>1</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>64</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1033,6 +1405,505 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6301DB66-69A8-3E44-86C1-38B39616905A}">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="18"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="18"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="18"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97831699-8ED8-B047-BDB8-038509C9D266}">
   <dimension ref="B9:E28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1074,13 +1945,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -1096,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1114,7 +1985,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1125,7 +1996,7 @@
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E18" s="3"/>
     </row>
@@ -1134,7 +2005,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="3"/>
@@ -1145,7 +2016,7 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -1154,11 +2025,11 @@
         <v>13</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
@@ -1167,7 +2038,7 @@
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -1178,7 +2049,7 @@
       <c r="C23" s="6"/>
       <c r="D23" s="7"/>
       <c r="E23" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
@@ -1187,7 +2058,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E24" s="5"/>
     </row>
@@ -1198,7 +2069,7 @@
       <c r="C25" s="6"/>
       <c r="D25" s="7"/>
       <c r="E25" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
@@ -1216,7 +2087,7 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
@@ -1232,31 +2103,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C4425D2-5FFA-4C4B-A495-A22788A789E5}">
   <dimension ref="B9:S29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="9" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>36</v>
-      </c>
       <c r="O9" s="12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
@@ -1268,32 +2139,32 @@
     </row>
     <row r="12" spans="2:19" ht="17" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="17" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="2:19" ht="17" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="2:19" ht="17" x14ac:dyDescent="0.25">
@@ -1301,132 +2172,132 @@
     </row>
     <row r="16" spans="2:19" ht="17" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="O18" s="11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="O20" s="11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B23" s="11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="O24" s="11"/>
     </row>
     <row r="26" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B26" s="11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="O27" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="2:15" ht="17" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="17" x14ac:dyDescent="0.25">

--- a/docs/modelling_approach.xlsx
+++ b/docs/modelling_approach.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johtorr/Documents/Repos/neural_networks_project_hdm/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F703579C-52D6-BB44-9625-CD27C9C95A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75201ABF-048E-4E4D-B265-9E850CC2335A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
     <sheet name="Tabelle4" sheetId="4" r:id="rId2"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId3"/>
-    <sheet name="Tabelle3" sheetId="3" r:id="rId4"/>
+    <sheet name="Tabelle5" sheetId="5" r:id="rId3"/>
+    <sheet name="Tabelle2" sheetId="2" r:id="rId4"/>
+    <sheet name="Tabelle3" sheetId="3" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tabelle5!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -555,6 +559,15 @@
   </si>
   <si>
     <t>Fold</t>
+  </si>
+  <si>
+    <t>Fold2</t>
+  </si>
+  <si>
+    <t>Fold3</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
@@ -704,10 +717,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1261,7 +1274,7 @@
       <c r="I21" t="s">
         <v>69</v>
       </c>
-      <c r="L21" s="18" t="s">
+      <c r="L21" s="17" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1269,7 +1282,7 @@
       <c r="B22" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="18" t="s">
+      <c r="L22" s="17" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1283,7 +1296,7 @@
       <c r="D23" t="s">
         <v>64</v>
       </c>
-      <c r="L23" s="18" t="s">
+      <c r="L23" s="17" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1297,7 +1310,7 @@
       <c r="D24" t="s">
         <v>82</v>
       </c>
-      <c r="L24" s="18" t="s">
+      <c r="L24" s="17" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1311,7 +1324,7 @@
       <c r="D25" t="s">
         <v>64</v>
       </c>
-      <c r="L25" s="18" t="s">
+      <c r="L25" s="17" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1325,7 +1338,7 @@
       <c r="D26" t="s">
         <v>82</v>
       </c>
-      <c r="L26" s="18" t="s">
+      <c r="L26" s="17" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1339,7 +1352,7 @@
       <c r="D27" t="s">
         <v>64</v>
       </c>
-      <c r="L27" s="18" t="s">
+      <c r="L27" s="17" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1353,7 +1366,7 @@
       <c r="D28" t="s">
         <v>82</v>
       </c>
-      <c r="L28" s="18" t="s">
+      <c r="L28" s="17" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1380,24 +1393,24 @@
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1468,7 +1481,7 @@
       <c r="D3" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="18"/>
+      <c r="K3" s="17"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1483,7 +1496,7 @@
       <c r="D4" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="18"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1498,7 +1511,7 @@
       <c r="D5" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="18"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1513,7 +1526,7 @@
       <c r="D6" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="18"/>
+      <c r="K6" s="17"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1528,7 +1541,7 @@
       <c r="D7" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -1543,7 +1556,7 @@
       <c r="D8" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="18"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1558,7 +1571,7 @@
       <c r="D9" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="18"/>
+      <c r="K9" s="17"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1573,7 +1586,7 @@
       <c r="D10" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="18"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1900,10 +1913,281 @@
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32C5334-F7E7-E34A-95A2-9690A23087D0}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1" xr:uid="{A32C5334-F7E7-E34A-95A2-9690A23087D0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I17">
+      <sortCondition descending="1" ref="B1:B17"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97831699-8ED8-B047-BDB8-038509C9D266}">
   <dimension ref="B9:E28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2103,7 +2387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C4425D2-5FFA-4C4B-A495-A22788A789E5}">
   <dimension ref="B9:S29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2126,13 +2410,13 @@
       <c r="H10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="O10" s="17" t="s">
+      <c r="O10" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.2">
       <c r="O11" s="14"/>

--- a/docs/modelling_approach.xlsx
+++ b/docs/modelling_approach.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/johtorr/Documents/Repos/neural_networks_project_hdm/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75201ABF-048E-4E4D-B265-9E850CC2335A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE46E32-8A35-E544-A2CA-B9D5D6535A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{234F4985-7325-E745-815C-EBE544E9734D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle4" sheetId="4" r:id="rId2"/>
-    <sheet name="Tabelle5" sheetId="5" r:id="rId3"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId4"/>
-    <sheet name="Tabelle3" sheetId="3" r:id="rId5"/>
+    <sheet name="Tabelle6" sheetId="6" r:id="rId2"/>
+    <sheet name="Tabelle4" sheetId="4" r:id="rId3"/>
+    <sheet name="Tabelle5" sheetId="5" r:id="rId4"/>
+    <sheet name="Tabelle2" sheetId="2" r:id="rId5"/>
+    <sheet name="Tabelle3" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Tabelle5!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Tabelle5!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -569,12 +570,54 @@
   <si>
     <t>Average</t>
   </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>werte</t>
+  </si>
+  <si>
+    <t>seq_0</t>
+  </si>
+  <si>
+    <t>embargo</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>n_seq</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>n_ts</t>
+  </si>
+  <si>
+    <t>seq_len = 6</t>
+  </si>
+  <si>
+    <t>Anzahl Werte</t>
+  </si>
+  <si>
+    <t>Unser</t>
+  </si>
+  <si>
+    <t>seq_ptr</t>
+  </si>
+  <si>
+    <t>ind_ptr</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = [0,5,…]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -644,6 +687,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -683,7 +733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -721,6 +771,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -736,6 +797,251 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>270935</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>135466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>406401</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>177799</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Pfeil nach unten 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE05022-2A31-2E4B-B19B-0B535C6351D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1930402" y="2980266"/>
+          <a:ext cx="135466" cy="245533"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>270934</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>118534</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>414867</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Pfeil nach unten 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA6AE02D-97A8-9B40-927A-E648ADB9A629}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1930401" y="1540934"/>
+          <a:ext cx="143933" cy="237066"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>101601</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>245534</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>135466</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Pfeil nach unten 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46BC2B52-E61B-5D46-BF13-FD57AC111AA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3826934" y="1524000"/>
+          <a:ext cx="143933" cy="237066"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>177801</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>135467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>321734</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>169333</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Pfeil nach unten 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2B71319-EBBE-B740-9857-56ACB4397BBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3903134" y="2980267"/>
+          <a:ext cx="143933" cy="237066"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="de-DE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1418,6 +1724,540 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D99AF7-B803-B94E-A1B1-BB65221D85BB}">
+  <dimension ref="B3:AM32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="5.83203125" customWidth="1"/>
+    <col min="4" max="6" width="4.6640625" customWidth="1"/>
+    <col min="7" max="7" width="7.1640625" customWidth="1"/>
+    <col min="8" max="11" width="4.6640625" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" customWidth="1"/>
+    <col min="13" max="39" width="4.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12">
+        <v>3</v>
+      </c>
+      <c r="G6" s="12">
+        <v>4</v>
+      </c>
+      <c r="H6" s="12">
+        <v>5</v>
+      </c>
+      <c r="I6" s="12">
+        <v>6</v>
+      </c>
+      <c r="J6" s="12">
+        <v>7</v>
+      </c>
+      <c r="K6" s="12">
+        <v>8</v>
+      </c>
+      <c r="L6" s="12">
+        <v>9</v>
+      </c>
+      <c r="M6" s="12">
+        <v>10</v>
+      </c>
+      <c r="N6" s="12">
+        <v>11</v>
+      </c>
+      <c r="O6" s="12">
+        <v>12</v>
+      </c>
+      <c r="P6" s="12">
+        <v>13</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>14</v>
+      </c>
+      <c r="R6" s="12">
+        <v>15</v>
+      </c>
+      <c r="S6" s="12">
+        <v>16</v>
+      </c>
+      <c r="T6" s="12">
+        <v>17</v>
+      </c>
+      <c r="U6" s="12">
+        <v>18</v>
+      </c>
+      <c r="V6" s="12">
+        <v>19</v>
+      </c>
+      <c r="W6" s="12">
+        <v>20</v>
+      </c>
+      <c r="X6" s="12">
+        <v>21</v>
+      </c>
+      <c r="Y6" s="12">
+        <v>22</v>
+      </c>
+      <c r="Z6" s="12">
+        <v>23</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>24</v>
+      </c>
+      <c r="AB6" s="12">
+        <v>25</v>
+      </c>
+      <c r="AC6" s="12">
+        <v>26</v>
+      </c>
+      <c r="AD6" s="12">
+        <v>27</v>
+      </c>
+      <c r="AE6" s="12">
+        <v>28</v>
+      </c>
+      <c r="AF6" s="12">
+        <v>29</v>
+      </c>
+      <c r="AG6" s="12">
+        <v>30</v>
+      </c>
+      <c r="AH6" s="12">
+        <v>31</v>
+      </c>
+      <c r="AI6" s="12">
+        <v>32</v>
+      </c>
+      <c r="AJ6" s="12">
+        <v>33</v>
+      </c>
+      <c r="AK6" s="12">
+        <v>34</v>
+      </c>
+      <c r="AL6" s="12">
+        <v>35</v>
+      </c>
+      <c r="AM6" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7">
+        <v>54.35140800443061</v>
+      </c>
+      <c r="D7">
+        <v>35.33388309338995</v>
+      </c>
+      <c r="E7">
+        <v>64.564400976904807</v>
+      </c>
+      <c r="F7">
+        <v>46.675532480520609</v>
+      </c>
+      <c r="G7">
+        <v>98.019236047454044</v>
+      </c>
+      <c r="H7">
+        <v>16.215380370327981</v>
+      </c>
+      <c r="I7">
+        <v>42.04215337253784</v>
+      </c>
+      <c r="J7">
+        <v>14.518657847401961</v>
+      </c>
+      <c r="K7">
+        <v>48.908431886108126</v>
+      </c>
+      <c r="L7">
+        <v>71.868439121801629</v>
+      </c>
+      <c r="M7">
+        <v>0.29499553394913836</v>
+      </c>
+      <c r="N7">
+        <v>4.2466535147250628</v>
+      </c>
+      <c r="O7">
+        <v>7.956683964226241</v>
+      </c>
+      <c r="P7">
+        <v>26.062326444868699</v>
+      </c>
+      <c r="Q7">
+        <v>3.7453259747186718</v>
+      </c>
+      <c r="R7">
+        <v>29.988373706843696</v>
+      </c>
+      <c r="S7">
+        <v>99.180935540977373</v>
+      </c>
+      <c r="T7">
+        <v>47.507261678877299</v>
+      </c>
+      <c r="U7">
+        <v>58.590639676054977</v>
+      </c>
+      <c r="V7">
+        <v>38.572709634242543</v>
+      </c>
+      <c r="W7">
+        <v>88.636005117498158</v>
+      </c>
+      <c r="X7">
+        <v>51.967676633315648</v>
+      </c>
+      <c r="Y7">
+        <v>69.195578062926117</v>
+      </c>
+      <c r="Z7">
+        <v>47.240101689434866</v>
+      </c>
+      <c r="AA7">
+        <v>12.45421443835818</v>
+      </c>
+      <c r="AB7">
+        <v>77.963139719389957</v>
+      </c>
+      <c r="AC7">
+        <v>58.029103945720053</v>
+      </c>
+      <c r="AD7">
+        <v>1.6514925584864781</v>
+      </c>
+      <c r="AE7">
+        <v>12.118328441671133</v>
+      </c>
+      <c r="AF7">
+        <v>76.483728443725681</v>
+      </c>
+      <c r="AG7">
+        <v>94.062947270064896</v>
+      </c>
+      <c r="AH7">
+        <v>40.559869408102202</v>
+      </c>
+      <c r="AI7">
+        <v>81.22599258224875</v>
+      </c>
+      <c r="AJ7">
+        <v>45.834224937434286</v>
+      </c>
+      <c r="AK7">
+        <v>84.836692873532655</v>
+      </c>
+      <c r="AL7">
+        <v>62.695318077818222</v>
+      </c>
+      <c r="AM7">
+        <v>72.243890753357121</v>
+      </c>
+    </row>
+    <row r="10" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="21">
+        <v>54.35140800443061</v>
+      </c>
+      <c r="D11">
+        <v>35.33388309338995</v>
+      </c>
+      <c r="E11">
+        <v>64.564400976904807</v>
+      </c>
+      <c r="F11">
+        <v>46.675532480520609</v>
+      </c>
+      <c r="G11" s="21">
+        <v>98.019236047454044</v>
+      </c>
+      <c r="H11">
+        <v>16.215380370327981</v>
+      </c>
+      <c r="L11" t="s">
+        <v>106</v>
+      </c>
+      <c r="M11" s="22">
+        <v>0</v>
+      </c>
+      <c r="N11" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="21">
+        <v>42.04215337253784</v>
+      </c>
+      <c r="G12" s="21"/>
+    </row>
+    <row r="13" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="21">
+        <v>14.518657847401961</v>
+      </c>
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="C14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="R14" t="s">
+        <v>107</v>
+      </c>
+      <c r="S14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="C15" s="21"/>
+      <c r="G15" s="21"/>
+    </row>
+    <row r="16" spans="2:39" x14ac:dyDescent="0.2">
+      <c r="C16" s="21"/>
+      <c r="G16" s="21"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="C17" s="12">
+        <v>1</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="21">
+        <v>35.33388309338995</v>
+      </c>
+      <c r="D18">
+        <v>64.564400976904807</v>
+      </c>
+      <c r="E18">
+        <v>46.675532480520609</v>
+      </c>
+      <c r="F18">
+        <v>98.019236047454044</v>
+      </c>
+      <c r="G18" s="21">
+        <v>16.215380370327981</v>
+      </c>
+      <c r="H18">
+        <v>42.04215337253784</v>
+      </c>
+      <c r="L18" t="s">
+        <v>106</v>
+      </c>
+      <c r="M18" s="22">
+        <v>1</v>
+      </c>
+      <c r="N18" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19">
+        <v>48.908431886108126</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="21">
+        <v>71.868439121801629</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="19">
+        <f>36-6-1</f>
+        <v>29</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="19">
+        <v>6</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24">
+        <f>29*6</f>
+        <v>174</v>
+      </c>
+      <c r="L24" t="s">
+        <v>100</v>
+      </c>
+      <c r="M24" s="19">
+        <f>36-6-1</f>
+        <v>29</v>
+      </c>
+      <c r="N24" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="19">
+        <v>2</v>
+      </c>
+      <c r="P24" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q24">
+        <f>29*2</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26">
+        <f>C25*G24</f>
+        <v>261348</v>
+      </c>
+      <c r="L26" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q26" s="23">
+        <f>C25*Q24</f>
+        <v>87116</v>
+      </c>
+      <c r="R26" s="23"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B29" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="19">
+        <f>93-6-1</f>
+        <v>86</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="19">
+        <v>6</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30">
+        <f>93*6</f>
+        <v>558</v>
+      </c>
+      <c r="L30" t="s">
+        <v>100</v>
+      </c>
+      <c r="M30" s="19">
+        <v>86</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O30" s="19">
+        <v>2</v>
+      </c>
+      <c r="P30" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q30">
+        <f>86*2</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32">
+        <f>C31*G30</f>
+        <v>838116</v>
+      </c>
+      <c r="L32" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q32" s="23">
+        <f>C31*Q30</f>
+        <v>258344</v>
+      </c>
+      <c r="R32" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="Q32:R32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6301DB66-69A8-3E44-86C1-38B39616905A}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1917,7 +2757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32C5334-F7E7-E34A-95A2-9690A23087D0}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2187,7 +3027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97831699-8ED8-B047-BDB8-038509C9D266}">
   <dimension ref="B9:E28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2387,7 +3227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C4425D2-5FFA-4C4B-A495-A22788A789E5}">
   <dimension ref="B9:S29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
